--- a/data/seed/portfolio/L-2025-7460/vypiska_2026-07_08.xlsx
+++ b/data/seed/portfolio/L-2025-7460/vypiska_2026-07_08.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -558,40 +558,40 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>8026000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>10915000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Denov Yog'och XK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>277273294</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000872935258001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №262/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №238/26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -601,38 +601,38 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>3830000</v>
+        <v>13050000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №117/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №262/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -641,22 +641,22 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5917000</v>
+        <v>10513000</v>
       </c>
       <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Denov Yog'och XK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>277273294</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000872935258001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -666,14 +666,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №250/26</t>
+          <t>Tovarlar uchun to'lov h/f №8893</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -682,34 +682,39 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>21304000</v>
+        <v>17311000</v>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Ilhom Meva Eksport MChJ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>207506886</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000941126206001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Tovarlar uchun to'lov h/f №1495</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -718,39 +723,34 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>59157000</v>
+        <v>21304000</v>
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>372772732</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8199</t>
+          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -764,34 +764,34 @@
       <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish Materiallari MChJ</t>
+          <t>Qo'qon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>223228608</t>
+          <t>353950053</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000469087048001</t>
+          <t>20208000821517437001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по договору №13/24</t>
+          <t>Ijara haqi iyul oyi uchun, shartn. №83/24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -799,40 +799,40 @@
           <t>106</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>9268000</v>
-      </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n">
+        <v>37893000</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ziyo Sut Mahsulotlari AJ</t>
+          <t>Durdona Logistik AJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>277698374</t>
+          <t>359203798</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000705665382001</t>
+          <t>20208000480906096001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №95/26, QQS bilan</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №25/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -840,40 +840,40 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>60876000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>30832000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №213/26, QQS bilan</t>
+          <t>Shartnoma №299/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -881,40 +881,40 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>8944000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>10366000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Andijon Polimer MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>255211459</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000401638839001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5419</t>
+          <t>Shartnoma №235/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -924,38 +924,38 @@
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>26049000</v>
+        <v>7407000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №68/26 от 10.07.2026</t>
+          <t>Shartnoma №30/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -965,21 +965,21 @@
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n">
-        <v>22256000</v>
+        <v>7055000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Navoiy Avto Savdo MChJ</t>
+          <t>Buxoro Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>295592037</t>
+          <t>206655171</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000864809060001</t>
+          <t>20208000558320322001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -989,14 +989,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1152 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3236</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1005,39 +1005,39 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>42950000</v>
+        <v>59467000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Xiva Qurilish Materiallari MChJ</t>
+          <t>Denov Yog'och XK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>297391804</t>
+          <t>277273294</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000422325263001</t>
+          <t>20208000872935258001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2804</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №33/26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1045,40 +1045,40 @@
           <t>112</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>30282000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>17581000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Farg'ona Poligraf MChJ</t>
+          <t>Olmaliq Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>344066551</t>
+          <t>315873903</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000195583203001</t>
+          <t>20208000532077712001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №3236 за поставленный товар</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №296/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1086,40 +1086,40 @@
           <t>113</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>8664000</v>
-      </c>
+      <c r="C23" s="2" t="n">
+        <v>44094000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Olmaliq Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>315873903</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000532077712001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №235/26 от 13.07.2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №18/26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1129,38 +1129,38 @@
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>7259000</v>
+        <v>12996000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Farg'ona Poligraf MChJ</t>
+          <t>Termiz Savdo MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>344066551</t>
+          <t>289421615</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000195583203001</t>
+          <t>20208000581869275001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1897</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2980 16.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1168,40 +1168,40 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>7025000</v>
-      </c>
+      <c r="C25" s="2" t="n">
+        <v>2905000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №299/26 от 13.07.2026</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1209,40 +1209,40 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>4942000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>2905000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Navoiy Avto Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>295592037</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000864809060001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №25/26, НДС 12%</t>
+          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1250,40 +1250,40 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>4250000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>60621000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Denov Yog'och XK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>277273294</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000872935258001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №253 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №34/26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1292,39 +1292,39 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>8240000</v>
+        <v>67418000</v>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Ilhom Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>207506886</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000941126206001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №160/26 от 13.07.2026, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №7814</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1332,40 +1332,40 @@
           <t>119</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>57331000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>23565000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5598</t>
+          <t>Mahsulot uchun to'lov, shartnoma №119/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1373,40 +1373,40 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>65537000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>15162000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chirchiq Agro Servis MChJ</t>
+          <t>Nihol Mebel MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>317975440</t>
+          <t>307157078</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000617072152001</t>
+          <t>20208000653301936001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №298/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4247</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1416,38 +1416,38 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>3899000</v>
+        <v>8198000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Farg'ona Poligraf MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>344066551</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000195583203001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №2946 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>SHARTNOMA №39/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1455,40 +1455,40 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>3764000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>19501000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Farg'ona Poligraf MChJ</t>
+          <t>Olmaliq Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>344066551</t>
+          <t>315873903</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000195583203001</t>
+          <t>20208000532077712001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8190 от 15.07.2026, в т.ч. НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №292/26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1496,23 +1496,23 @@
           <t>123</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>5425000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>27668000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Ilhom Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>207506886</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000941126206001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1522,14 +1522,14 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7191 от 16.07.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №233/26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1538,39 +1538,34 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>2905000</v>
+        <v>40500000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-7460)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000381009430417</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Kredit shartnomasi L-2025-7460 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1578,40 +1573,40 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>2905000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>12487000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>НДФЛ за июнь 2026</t>
+          <t>Mahsulot uchun to'lov, shartn. №46/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1619,40 +1614,40 @@
           <t>126</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>26076000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>5341000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Navoiy Avto Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>295592037</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000864809060001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Shartnoma №140/26 bo'yicha oldindan to'lov</t>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1662,38 +1657,38 @@
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>10355000</v>
+        <v>76474000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №95/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9392</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1703,38 +1698,38 @@
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>9464000</v>
+        <v>75297000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №119/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6933</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1742,35 +1737,40 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>40500000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>12309000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-7460)</t>
+          <t>Urganch Qurilish Materiallari XK</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>368093183</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>16307000381009430417</t>
+          <t>20208000737626312001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-7460 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2997</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1780,38 +1780,38 @@
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>31581000</v>
+        <v>50192000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №46/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №171/26 от 27.07.2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1821,21 +1821,21 @@
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>11837000</v>
+        <v>13572000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Marg'ilon Metall MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>269071570</t>
+          <t>382331177</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000856533019001</t>
+          <t>20208000642922264001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1845,14 +1845,14 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №269/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №374</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1860,40 +1860,40 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n">
-        <v>12073000</v>
-      </c>
+      <c r="C42" s="2" t="n">
+        <v>1994000</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Farg'ona Poligraf MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>344066551</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000195583203001</t>
+          <t>20208000047367181001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №70/26, НДС 12%</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1901,40 +1901,40 @@
           <t>133</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n">
-        <v>8225000</v>
-      </c>
+      <c r="C43" s="2" t="n">
+        <v>15891000</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Denov Tur Servis XK</t>
+          <t>Denov Yog'och XK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>368680931</t>
+          <t>277273294</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000397376263001</t>
+          <t>20208000872935258001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2997 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №248/26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1942,23 +1942,23 @@
           <t>134</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>8056000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>21805000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Ilhom Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>207506886</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000941126206001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1968,14 +1968,14 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9392 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №212/26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,23 +1983,23 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>5845000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>11561000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Ilhom Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>207506886</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000941126206001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2009,14 +2009,14 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6933 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №1/26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2024,40 +2024,40 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>5152000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>38262000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Buxoro Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>206655171</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000558320322001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №8205 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2066,39 +2066,34 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>21366000</v>
+        <v>300000</v>
       </c>
       <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bunyodkor Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>255471730</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000998687831001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №181/26</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2108,38 +2103,38 @@
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>71374000</v>
+        <v>1381000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bog'ishamol Avto Ehtiyot XK</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>213894216</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000565818692001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2980 от 24.07.2026, в т.ч. НДС 12%</t>
+          <t>SHARTNOMA№235/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2147,40 +2142,40 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>11793000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>4132000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Denov Yog'och XK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>277273294</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000872935258001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №156/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №5935</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2190,38 +2185,38 @@
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>4863000</v>
+        <v>2131000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Farg'ona Poligraf MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>344066551</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000195583203001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2596</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9631</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2231,38 +2226,38 @@
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>4093000</v>
+        <v>1057000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Buxoro Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>206655171</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000558320322001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4473 от 24.07.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №182/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2270,40 +2265,35 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n">
-        <v>6727000</v>
-      </c>
+      <c r="C52" s="2" t="n">
+        <v>20427000</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Qarshi Plastik AJ</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>355823311</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000776429222001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №374 за поставленный товар</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2311,23 +2301,23 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>1994000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>3537000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000581080089001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2337,14 +2327,14 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за июль 2026 г.</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3553</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2353,39 +2343,39 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>31846000</v>
+        <v>1796000</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Denov Yog'och XK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>336718189</t>
+          <t>277273294</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000061580832001</t>
+          <t>20208000872935258001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №252/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №294/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2393,23 +2383,23 @@
           <t>145</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>8559000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>3491000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chirchiq Agro Servis MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>317975440</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000617072152001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2419,14 +2409,14 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8941</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1654 07.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2434,23 +2424,23 @@
           <t>146</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n">
-        <v>9586000</v>
-      </c>
+      <c r="C56" s="2" t="n">
+        <v>3360000</v>
+      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Ilhom Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>207506886</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000941126206001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2460,14 +2450,14 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2486 от 30.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №42/26</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2477,38 +2467,38 @@
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n">
-        <v>55225000</v>
+        <v>3438000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №9/26 от 31.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №160/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2518,38 +2508,38 @@
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>6503000</v>
+        <v>3430000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Farg'ona Poligraf MChJ</t>
+          <t>Buxoro Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>344066551</t>
+          <t>206655171</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000195583203001</t>
+          <t>20208000558320322001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9623</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №78/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2557,35 +2547,40 @@
           <t>149</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>2077000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Shartnoma №135/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2595,38 +2590,38 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>14449000</v>
+        <v>2071000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bog'ishamol Avto Ehtiyot XK</t>
+          <t>Nihol Mebel MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>213894216</t>
+          <t>307157078</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000565818692001</t>
+          <t>20208000653301936001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2569 за поставленный товар</t>
+          <t>Предоплата за товар по дог. №34/26 от 10.08.2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2636,38 +2631,38 @@
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>4576000</v>
+        <v>1842000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1923 за поставленный товар</t>
+          <t>Shartnoma №102/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2676,39 +2671,39 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>3364000</v>
+        <v>3059000</v>
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Qo'qon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>353950053</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000821517437001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №240/26 от 03.08.2026, НДС 12%</t>
+          <t>Ijara haqi avgust oyi uchun, shartn. №83/24</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2717,22 +2712,22 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>5575000</v>
+        <v>3065000</v>
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Denov Yog'och XK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>277273294</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000872935258001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2742,14 +2737,14 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №234/26</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №6485</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2757,40 +2752,40 @@
           <t>154</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>2178000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>8713000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №283/26</t>
+          <t>Shartnoma №221/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2798,40 +2793,40 @@
           <t>155</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>15113000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>5587000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Durdona Logistik AJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>359203798</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000480906096001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №13/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4920</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2839,40 +2834,40 @@
           <t>156</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>82398000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>4575000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>336718189</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000061580832001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6377</t>
+          <t>Оплата по счет-фактуре №172 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2882,38 +2877,38 @@
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>21091000</v>
+        <v>12926000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Navoiy Avto Savdo MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>295592037</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000864809060001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №297 от 05.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №52/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2923,38 +2918,38 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>99855000</v>
+        <v>8904000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Urganch Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>368093183</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000737626312001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6552 от 06.08.2026, в т.ч. НДС 12%</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №7252 13.08.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2964,38 +2959,38 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>12371000</v>
+        <v>1644000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Denov Tur Servis XK</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>368680931</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000397376263001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №755 от 06.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №123/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3003,35 +2998,40 @@
           <t>160</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>20427000</v>
-      </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n">
+        <v>9016000</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Durdona Logistik AJ</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>359203798</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000480906096001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №1589</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8451</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3039,40 +3039,40 @@
           <t>161</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>96400000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>2947000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №116/26</t>
+          <t>Shartnoma №217/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3082,38 +3082,38 @@
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>71815000</v>
+        <v>1152000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4661 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5995 14.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3121,40 +3121,40 @@
           <t>163</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>12739000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>2117000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Shahrisabz Agro Servis XK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>369837417</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000566538239001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №263/26 от 10.08.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №201/26</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3162,40 +3162,40 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>10241000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>2785000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №136 за поставленный товар</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3204,39 +3204,39 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>2409000</v>
+        <v>2785000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>366158739</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000305320777001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5870</t>
+          <t>JShDS iyul oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3245,39 +3245,39 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>3059000</v>
+        <v>27257000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish Materiallari MChJ</t>
+          <t>Ilhom Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>223228608</t>
+          <t>207506886</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000469087048001</t>
+          <t>20208000941126206001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №13/24</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №269/26</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3285,40 +3285,40 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>11248000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>3867000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Durdona Logistik AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>359203798</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000480906096001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №187/26</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №110/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3328,31 +3328,31 @@
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>47939000</v>
+        <v>3365000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Navoiy Avto Savdo MChJ</t>
+          <t>Durdona Logistik AJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>295592037</t>
+          <t>359203798</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000864809060001</t>
+          <t>20208000480906096001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №225/26 от 12.08.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №27/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -3367,33 +3367,33 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>6346000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>12139000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Samarqand Polimer MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>397544046</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000707215256001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №289/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №260/26 от 17.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3409,32 +3409,32 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>2785000</v>
+        <v>40373000</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Denov Yog'och XK</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>277273294</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000872935258001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
+          <t>Предоплата за материалы по договору №162/26</t>
         </is>
       </c>
     </row>
@@ -3450,39 +3450,39 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>2785000</v>
+        <v>175199000</v>
       </c>
       <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Samarqand Polimer MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>397544046</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000707215256001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №18/26</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3490,23 +3490,23 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>3339000</v>
-      </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n">
+        <v>3833000</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Sarbon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>285794333</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000741238648001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5484</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8450 18.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -3533,31 +3533,31 @@
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>19211000</v>
+        <v>2441000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №273/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №7737 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -3572,40 +3572,40 @@
           <t>174</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>3674000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>2054000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №2058</t>
+          <t>Оплата по счет-фактуре №2088 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3613,40 +3613,40 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>6224000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>1286000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Durdona Logistik AJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>359203798</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000480906096001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3397</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2985 18.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3654,35 +3654,40 @@
           <t>176</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>40500000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>1172000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-7460)</t>
+          <t>Buxoro Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>206655171</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>16307000381009430417</t>
+          <t>20208000558320322001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-7460 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Tovar uchun to'lov, h/f №7686 18.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3692,38 +3697,38 @@
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>6574000</v>
+        <v>4846000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Andijon Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>325923331</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000130317899001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4673 от 21.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №3372 19.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,38 +3738,38 @@
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>6162000</v>
+        <v>2005000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7866 за поставленный товар</t>
+          <t>Shartnoma №281/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3774,38 +3779,38 @@
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>4756000</v>
+        <v>1657000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Nihol Mebel MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>307157078</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000653301936001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №100/26 от 21.08.2026</t>
+          <t>Shartnoma №59/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3813,40 +3818,40 @@
           <t>180</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>3394000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>8106000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>336718189</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000061580832001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №50/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №91/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3855,32 +3860,27 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>10784000</v>
+        <v>40500000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>372772732</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-7460)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>16307000381009430417</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1072</t>
+          <t>Kredit shartnomasi L-2025-7460 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
@@ -3896,22 +3896,22 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>14061000</v>
+        <v>4697000</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Denov Yog'och XK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>277273294</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000872935258001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №9396</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №234/26</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3936,33 +3936,33 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>8857000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>4968000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Qarshi Plastik AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>355823311</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000776429222001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №40/26, НДС 12%</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
     </row>
@@ -3977,33 +3977,33 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>5054000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>19687000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Mahsulot uchun to'lov, shartnoma №259/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -4018,33 +4018,33 @@
           <t>185</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>7730000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>2060000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №209/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8710</t>
         </is>
       </c>
     </row>
@@ -4059,23 +4059,23 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>26864000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>1972000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chirchiq Agro Servis MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>317975440</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000617072152001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4085,14 +4085,14 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №81/26, QQS BILAN</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3476 24.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4102,38 +4102,38 @@
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>34093000</v>
+        <v>1203000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Farg'ona Poligraf MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>344066551</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000195583203001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8054 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №2418 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4141,40 +4141,40 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>5713000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>1160000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>336718189</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000061580832001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1087</t>
+          <t>Mahsulot uchun to'lov, shartnoma №12/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4183,39 +4183,39 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>9251000</v>
+        <v>2895000</v>
       </c>
       <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Xiva Qurilish Materiallari MChJ</t>
+          <t>Denov Yog'och XK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>297391804</t>
+          <t>277273294</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000422325263001</t>
+          <t>20208000872935258001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4082</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №209/26</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4239,24 +4239,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000581080089001</t>
+          <t>20208000047367181001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за август 2026 г.</t>
+          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ ОГЛАСНО СЧЕТУ</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4264,40 +4264,40 @@
           <t>191</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>6958000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>1797000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Durdona Logistik AJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>359203798</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000480906096001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №7058</t>
+          <t>Оплата за товар по с/ф №6467 от 27.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4305,23 +4305,23 @@
           <t>192</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>19885000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>1698000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Xiva Qurilish Materiallari MChJ</t>
+          <t>Nihol Mebel MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>297391804</t>
+          <t>307157078</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000422325263001</t>
+          <t>20208000653301936001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4331,14 +4331,14 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3570</t>
+          <t>Mahsulot uchun to'lov, shartnoma №296/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4348,38 +4348,38 @@
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>26519000</v>
+        <v>1136000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Navoiy Avto Savdo MChJ</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>295592037</t>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000864809060001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4675</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8124</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4387,40 +4387,40 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>7199000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>5766000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Denov Yog'och XK</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>277273294</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000872935258001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №256/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №284/26</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4428,40 +4428,40 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n">
-        <v>6379000</v>
-      </c>
+      <c r="C105" s="2" t="n">
+        <v>8283000</v>
+      </c>
+      <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Farovon Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>334124720</t>
+          <t>321145984</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000833274022001</t>
+          <t>20208000163883931001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №162/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №246/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4469,35 +4469,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>16352000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>212472088</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000327402267001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата за продукцию по договору №49/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4505,59 +4510,464 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>21993000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>7359000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bahor Mebel AJ</t>
+          <t>Nihol Mebel MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>372772732</t>
+          <t>307157078</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000498729352001</t>
+          <t>20208000653301936001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №235/26 ОТ 31.08.2026, НДС 12%</t>
+          <t>Shartnoma №275/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="n">
-        <v>893619000</v>
-      </c>
-      <c r="D108" s="4" t="n">
-        <v>850519000</v>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>2809000</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Zarafshon Meva Eksport AJ</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>339180454</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>20208000232526346001</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №9447</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>6476000</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Denov Yog'och XK</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>277273294</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>20208000872935258001</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №239/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>243485000</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Ilhom Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>212472088</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>20208000327402267001</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1698</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>1508000</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Durdona Logistik AJ</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>359203798</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>20208000480906096001</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №7759 31.08.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Oqsaroy Bank ATB</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Bank xizmati uchun komissiya</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>1860000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Denov Yog'och XK</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>277273294</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>20208000872935258001</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartn. №15/26, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>2245000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Olmaliq Ip-Kalava MChJ</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>315873903</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>20208000532077712001</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartnoma №16/26, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>2532000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Ilhom Meva Eksport MChJ</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>207506886</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>20208000941126206001</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №7747</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>2956000</v>
+      </c>
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Olmaliq Ip-Kalava MChJ</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>315873903</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>20208000532077712001</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по договору №11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>52706000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Zarafshon Meva Eksport AJ</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>339180454</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>20208000232526346001</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartn. №51/26, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>902185000</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>859085000</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C109" s="4" t="n">
+      <c r="C119" s="4" t="n">
         <v>239300000</v>
       </c>
-      <c r="D109" s="4" t="n"/>
+      <c r="D119" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
